--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 王明</t>
+          <t>月嫂撥款 高芳</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 黃婷</t>
+          <t>月嫂撥款 李翔英</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 劉偉安</t>
+          <t>月嫂撥款 林豪</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 高傑宇</t>
+          <t>月嫂撥款 李威</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 陳茹</t>
+          <t>月嫂撥款 林君</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>王明</t>
+          <t>高芳</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>王明</t>
+          <t>高芳</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>黃婷</t>
+          <t>李翔英</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>黃婷</t>
+          <t>李翔英</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>劉偉安</t>
+          <t>林豪</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>劉偉安</t>
+          <t>林豪</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>高傑宇</t>
+          <t>李威</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>高傑宇</t>
+          <t>李威</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>陳茹</t>
+          <t>林君</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>陳茹</t>
+          <t>林君</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>胡明</t>
+          <t>許晴</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>胡明</t>
+          <t>許晴</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>郭翔</t>
+          <t>郭安</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>郭翔</t>
+          <t>郭安</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>周晴</t>
+          <t>王翔</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>周晴</t>
+          <t>王翔</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>賴宥</t>
+          <t>李嘉</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>賴宥</t>
+          <t>李嘉</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>黃美雅</t>
+          <t>高洋</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>黃美雅</t>
+          <t>高洋</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -530,10 +530,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="I3" t="n">
-        <v>512000</v>
+        <v>502000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>68000</v>
+        <v>28000</v>
       </c>
       <c r="I4" t="n">
-        <v>580000</v>
+        <v>530000</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>60000</v>
+        <v>25500</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>520000</v>
+        <v>504500</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 高芳</t>
+          <t>月嫂撥款 張芳</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -665,10 +665,10 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="I6" t="n">
-        <v>532000</v>
+        <v>507000</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>68000</v>
+        <v>35000</v>
       </c>
       <c r="I7" t="n">
-        <v>600000</v>
+        <v>542000</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -754,15 +754,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>60000</v>
+        <v>31875</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>540000</v>
+        <v>510125</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 李翔英</t>
+          <t>月嫂撥款 楊琪</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -800,10 +800,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="I9" t="n">
-        <v>552000</v>
+        <v>514125</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>68000</v>
+        <v>26000</v>
       </c>
       <c r="I10" t="n">
-        <v>620000</v>
+        <v>540125</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>60000</v>
+        <v>25500</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>560000</v>
+        <v>514625</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 林豪</t>
+          <t>月嫂撥款 張涵</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -935,10 +935,10 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>12000</v>
+        <v>4400</v>
       </c>
       <c r="I12" t="n">
-        <v>572000</v>
+        <v>519025</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>68000</v>
+        <v>61600</v>
       </c>
       <c r="I13" t="n">
-        <v>640000</v>
+        <v>580625</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>60000</v>
+        <v>56100</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>580000</v>
+        <v>524525</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 李威</t>
+          <t>月嫂撥款 周雅</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="I15" t="n">
-        <v>592000</v>
+        <v>527025</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>68000</v>
+        <v>35000</v>
       </c>
       <c r="I16" t="n">
-        <v>660000</v>
+        <v>562025</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>60000</v>
+        <v>31875</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>600000</v>
+        <v>530150</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 林君</t>
+          <t>月嫂撥款 張宇</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="I18" t="n">
-        <v>612000</v>
+        <v>534150</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>68000</v>
+        <v>36000</v>
       </c>
       <c r="I19" t="n">
-        <v>680000</v>
+        <v>570150</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="I20" t="n">
-        <v>692000</v>
+        <v>574150</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>68000</v>
+        <v>26000</v>
       </c>
       <c r="I21" t="n">
-        <v>760000</v>
+        <v>600150</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="I22" t="n">
-        <v>772000</v>
+        <v>605150</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="I23" t="n">
-        <v>784000</v>
+        <v>607150</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="I24" t="n">
-        <v>796000</v>
+        <v>609150</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>2500</v>
       </c>
       <c r="I25" t="n">
-        <v>798500</v>
+        <v>611650</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>15000</v>
       </c>
       <c r="I26" t="n">
-        <v>813500</v>
+        <v>626650</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>3000</v>
       </c>
       <c r="I27" t="n">
-        <v>816500</v>
+        <v>629650</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>高芳</t>
+          <t>張芳</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1682,14 +1682,14 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="J1" t="n">
-        <v>60000</v>
+        <v>25500</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>高芳</t>
+          <t>張芳</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>李翔英</t>
+          <t>楊琪</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1732,14 +1732,14 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>80000</v>
+        <v>37500</v>
       </c>
       <c r="J2" t="n">
-        <v>60000</v>
+        <v>31875</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>李翔英</t>
+          <t>楊琪</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>林豪</t>
+          <t>張涵</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1782,14 +1782,14 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>60000</v>
+        <v>25500</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>林豪</t>
+          <t>張涵</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>李威</t>
+          <t>周雅</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1832,14 +1832,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>80000</v>
+        <v>66000</v>
       </c>
       <c r="J4" t="n">
-        <v>60000</v>
+        <v>56100</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>李威</t>
+          <t>周雅</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>林君</t>
+          <t>張宇</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>80000</v>
+        <v>37500</v>
       </c>
       <c r="J5" t="n">
-        <v>60000</v>
+        <v>31875</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>林君</t>
+          <t>張宇</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>許晴</t>
+          <t>吳廷</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="J6" t="n">
-        <v>60000</v>
+        <v>34000</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>許晴</t>
+          <t>吳廷</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>郭安</t>
+          <t>吳冠</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1982,14 +1982,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="J7" t="n">
-        <v>60000</v>
+        <v>25500</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>郭安</t>
+          <t>吳冠</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>王翔</t>
+          <t>郭欣</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>80000</v>
+        <v>37500</v>
       </c>
       <c r="J8" t="n">
-        <v>60000</v>
+        <v>31875</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>王翔</t>
+          <t>郭欣</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>李嘉</t>
+          <t>陳俊英</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2082,14 +2082,14 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>80000</v>
+        <v>60000</v>
       </c>
       <c r="J9" t="n">
-        <v>60000</v>
+        <v>51000</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>李嘉</t>
+          <t>陳俊英</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>高洋</t>
+          <t>李強宏</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2132,14 +2132,14 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="J10" t="n">
-        <v>60000</v>
+        <v>42500</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>高洋</t>
+          <t>李強宏</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -530,10 +530,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I3" t="n">
-        <v>502000</v>
+        <v>502500</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>28000</v>
+        <v>72500</v>
       </c>
       <c r="I4" t="n">
-        <v>530000</v>
+        <v>575000</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25500</v>
+        <v>63750</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>504500</v>
+        <v>511250</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 張芳</t>
+          <t>月嫂撥款 趙偉洋</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -668,7 +668,7 @@
         <v>2500</v>
       </c>
       <c r="I6" t="n">
-        <v>507000</v>
+        <v>513750</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="I7" t="n">
-        <v>542000</v>
+        <v>573750</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -754,15 +754,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>31875</v>
+        <v>53125</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>510125</v>
+        <v>520625</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 楊琪</t>
+          <t>月嫂撥款 劉傑廷</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -800,10 +800,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="I9" t="n">
-        <v>514125</v>
+        <v>523125</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>26000</v>
+        <v>35000</v>
       </c>
       <c r="I10" t="n">
-        <v>540125</v>
+        <v>558125</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>25500</v>
+        <v>31875</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>514625</v>
+        <v>526250</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 張涵</t>
+          <t>月嫂撥款 趙美</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -935,10 +935,10 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>4400</v>
+        <v>2200</v>
       </c>
       <c r="I12" t="n">
-        <v>519025</v>
+        <v>528450</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>61600</v>
+        <v>63800</v>
       </c>
       <c r="I13" t="n">
-        <v>580625</v>
+        <v>592250</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1028,11 +1028,11 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>524525</v>
+        <v>536150</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 周雅</t>
+          <t>月嫂撥款 郭宏</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I15" t="n">
-        <v>527025</v>
+        <v>538150</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="I16" t="n">
-        <v>562025</v>
+        <v>576150</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>31875</v>
+        <v>34000</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>530150</v>
+        <v>542150</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 張宇</t>
+          <t>月嫂撥款 楊萱君</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I18" t="n">
-        <v>534150</v>
+        <v>547150</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>36000</v>
+        <v>32500</v>
       </c>
       <c r="I19" t="n">
-        <v>570150</v>
+        <v>579650</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>4000</v>
+        <v>2200</v>
       </c>
       <c r="I20" t="n">
-        <v>574150</v>
+        <v>581850</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>26000</v>
+        <v>52800</v>
       </c>
       <c r="I21" t="n">
-        <v>600150</v>
+        <v>634650</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="I22" t="n">
-        <v>605150</v>
+        <v>636650</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2000</v>
+        <v>4400</v>
       </c>
       <c r="I23" t="n">
-        <v>607150</v>
+        <v>641050</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I24" t="n">
-        <v>609150</v>
+        <v>643550</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>2500</v>
       </c>
       <c r="I25" t="n">
-        <v>611650</v>
+        <v>646050</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>15000</v>
       </c>
       <c r="I26" t="n">
-        <v>626650</v>
+        <v>661050</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>3000</v>
       </c>
       <c r="I27" t="n">
-        <v>629650</v>
+        <v>664050</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>張芳</t>
+          <t>趙偉洋</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1682,14 +1682,14 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>30000</v>
+        <v>75000</v>
       </c>
       <c r="J1" t="n">
-        <v>25500</v>
+        <v>63750</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>張芳</t>
+          <t>趙偉洋</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>楊琪</t>
+          <t>劉傑廷</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1732,14 +1732,14 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>37500</v>
+        <v>62500</v>
       </c>
       <c r="J2" t="n">
-        <v>31875</v>
+        <v>53125</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>楊琪</t>
+          <t>劉傑廷</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>張涵</t>
+          <t>趙美</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1782,14 +1782,14 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>30000</v>
+        <v>37500</v>
       </c>
       <c r="J3" t="n">
-        <v>25500</v>
+        <v>31875</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>張涵</t>
+          <t>趙美</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>周雅</t>
+          <t>郭宏</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>周雅</t>
+          <t>郭宏</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>張宇</t>
+          <t>楊萱君</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>37500</v>
+        <v>40000</v>
       </c>
       <c r="J5" t="n">
-        <v>31875</v>
+        <v>34000</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>張宇</t>
+          <t>楊萱君</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>吳廷</t>
+          <t>楊婷強</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>40000</v>
+        <v>37500</v>
       </c>
       <c r="J6" t="n">
-        <v>34000</v>
+        <v>31875</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>吳廷</t>
+          <t>楊婷強</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>吳冠</t>
+          <t>林嘉</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1982,14 +1982,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30000</v>
+        <v>55000</v>
       </c>
       <c r="J7" t="n">
-        <v>25500</v>
+        <v>46750</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>吳冠</t>
+          <t>林嘉</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>郭欣</t>
+          <t>張芳</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>37500</v>
+        <v>50000</v>
       </c>
       <c r="J8" t="n">
-        <v>31875</v>
+        <v>42500</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>郭欣</t>
+          <t>張芳</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>陳俊英</t>
+          <t>楊俊</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2082,14 +2082,14 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>60000</v>
+        <v>33000</v>
       </c>
       <c r="J9" t="n">
-        <v>51000</v>
+        <v>28050</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>陳俊英</t>
+          <t>楊俊</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>李強宏</t>
+          <t>吳雅明</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2132,14 +2132,14 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>50000</v>
+        <v>62500</v>
       </c>
       <c r="J10" t="n">
-        <v>42500</v>
+        <v>53125</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>李強宏</t>
+          <t>吳雅明</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 王明</t>
+          <t>月嫂撥款 郭強琪</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 黃婷</t>
+          <t>月嫂撥款 趙雅廷</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 劉偉安</t>
+          <t>月嫂撥款 李欣</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 高傑宇</t>
+          <t>月嫂撥款 許威</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 陳茹</t>
+          <t>月嫂撥款 劉偉</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>王明</t>
+          <t>郭強琪</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>王明</t>
+          <t>郭強琪</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>黃婷</t>
+          <t>趙雅廷</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>黃婷</t>
+          <t>趙雅廷</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>劉偉安</t>
+          <t>李欣</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>劉偉安</t>
+          <t>李欣</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>高傑宇</t>
+          <t>許威</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>高傑宇</t>
+          <t>許威</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>陳茹</t>
+          <t>劉偉</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>陳茹</t>
+          <t>劉偉</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>胡明</t>
+          <t>趙洋</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>胡明</t>
+          <t>趙洋</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>郭翔</t>
+          <t>吳欣</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>郭翔</t>
+          <t>吳欣</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>周晴</t>
+          <t>許芳</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>周晴</t>
+          <t>許芳</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>賴宥</t>
+          <t>徐宇傑</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>賴宥</t>
+          <t>徐宇傑</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>黃美雅</t>
+          <t>趙強奕</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>黃美雅</t>
+          <t>趙強奕</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -530,10 +530,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="I3" t="n">
-        <v>502500</v>
+        <v>504000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>72500</v>
+        <v>36000</v>
       </c>
       <c r="I4" t="n">
-        <v>575000</v>
+        <v>540000</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>63750</v>
+        <v>34000</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>511250</v>
+        <v>506000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 趙偉洋</t>
+          <t>月嫂撥款 吳晴宇</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -668,7 +668,7 @@
         <v>2500</v>
       </c>
       <c r="I6" t="n">
-        <v>513750</v>
+        <v>508500</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="I7" t="n">
-        <v>573750</v>
+        <v>543500</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -754,15 +754,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>53125</v>
+        <v>31875</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>520625</v>
+        <v>511625</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 劉傑廷</t>
+          <t>月嫂撥款 劉芳偉</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -800,10 +800,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="I9" t="n">
-        <v>523125</v>
+        <v>515625</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>35000</v>
+        <v>56000</v>
       </c>
       <c r="I10" t="n">
-        <v>558125</v>
+        <v>571625</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>31875</v>
+        <v>51000</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>526250</v>
+        <v>520625</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 趙美</t>
+          <t>月嫂撥款 林欣</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -935,10 +935,10 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="I12" t="n">
-        <v>528450</v>
+        <v>522625</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>63800</v>
+        <v>58000</v>
       </c>
       <c r="I13" t="n">
-        <v>592250</v>
+        <v>580625</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>56100</v>
+        <v>51000</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>536150</v>
+        <v>529625</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 郭宏</t>
+          <t>月嫂撥款 賴華萱</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>2000</v>
+        <v>4400</v>
       </c>
       <c r="I15" t="n">
-        <v>538150</v>
+        <v>534025</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>38000</v>
+        <v>39600</v>
       </c>
       <c r="I16" t="n">
-        <v>576150</v>
+        <v>573625</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>34000</v>
+        <v>37400</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>542150</v>
+        <v>536225</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 楊萱君</t>
+          <t>月嫂撥款 林俊美</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>5000</v>
+        <v>2200</v>
       </c>
       <c r="I18" t="n">
-        <v>547150</v>
+        <v>538425</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>32500</v>
+        <v>52800</v>
       </c>
       <c r="I19" t="n">
-        <v>579650</v>
+        <v>591225</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2200</v>
+        <v>4400</v>
       </c>
       <c r="I20" t="n">
-        <v>581850</v>
+        <v>595625</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>52800</v>
+        <v>61600</v>
       </c>
       <c r="I21" t="n">
-        <v>634650</v>
+        <v>657225</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="I22" t="n">
-        <v>636650</v>
+        <v>661225</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="I23" t="n">
-        <v>641050</v>
+        <v>663725</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>2500</v>
+        <v>4400</v>
       </c>
       <c r="I24" t="n">
-        <v>643550</v>
+        <v>668125</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>2500</v>
       </c>
       <c r="I25" t="n">
-        <v>646050</v>
+        <v>670625</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>15000</v>
       </c>
       <c r="I26" t="n">
-        <v>661050</v>
+        <v>685625</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>3000</v>
       </c>
       <c r="I27" t="n">
-        <v>664050</v>
+        <v>688625</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>趙偉洋</t>
+          <t>吳晴宇</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1682,14 +1682,14 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>75000</v>
+        <v>40000</v>
       </c>
       <c r="J1" t="n">
-        <v>63750</v>
+        <v>34000</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>趙偉洋</t>
+          <t>吳晴宇</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>劉傑廷</t>
+          <t>劉芳偉</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1732,14 +1732,14 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>62500</v>
+        <v>37500</v>
       </c>
       <c r="J2" t="n">
-        <v>53125</v>
+        <v>31875</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>劉傑廷</t>
+          <t>劉芳偉</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>趙美</t>
+          <t>林欣</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1782,14 +1782,14 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>37500</v>
+        <v>60000</v>
       </c>
       <c r="J3" t="n">
-        <v>31875</v>
+        <v>51000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>趙美</t>
+          <t>林欣</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>郭宏</t>
+          <t>賴華萱</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1832,14 +1832,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>66000</v>
+        <v>60000</v>
       </c>
       <c r="J4" t="n">
-        <v>56100</v>
+        <v>51000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>郭宏</t>
+          <t>賴華萱</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>楊萱君</t>
+          <t>林俊美</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>40000</v>
+        <v>44000</v>
       </c>
       <c r="J5" t="n">
-        <v>34000</v>
+        <v>37400</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>楊萱君</t>
+          <t>林俊美</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>楊婷強</t>
+          <t>林強</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>37500</v>
+        <v>55000</v>
       </c>
       <c r="J6" t="n">
-        <v>31875</v>
+        <v>46750</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>楊婷強</t>
+          <t>林強</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>林嘉</t>
+          <t>蔡雅</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1982,14 +1982,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>55000</v>
+        <v>66000</v>
       </c>
       <c r="J7" t="n">
-        <v>46750</v>
+        <v>56100</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>林嘉</t>
+          <t>蔡雅</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>張芳</t>
+          <t>賴晴</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="J8" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>張芳</t>
+          <t>賴晴</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>楊俊</t>
+          <t>吳明強</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2082,14 +2082,14 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>33000</v>
+        <v>75000</v>
       </c>
       <c r="J9" t="n">
-        <v>28050</v>
+        <v>63750</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>楊俊</t>
+          <t>吳明強</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>吳雅明</t>
+          <t>李安俊</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2132,14 +2132,14 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>62500</v>
+        <v>44000</v>
       </c>
       <c r="J10" t="n">
-        <v>53125</v>
+        <v>37400</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>吳雅明</t>
+          <t>李安俊</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -530,10 +530,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="I3" t="n">
-        <v>502500</v>
+        <v>502200</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>72500</v>
+        <v>41800</v>
       </c>
       <c r="I4" t="n">
-        <v>575000</v>
+        <v>544000</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>63750</v>
+        <v>37400</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>511250</v>
+        <v>506600</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 趙偉洋</t>
+          <t>月嫂撥款 李傑俊</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -665,10 +665,10 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="I6" t="n">
-        <v>513750</v>
+        <v>508800</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>60000</v>
+        <v>63800</v>
       </c>
       <c r="I7" t="n">
-        <v>573750</v>
+        <v>572600</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -754,15 +754,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>53125</v>
+        <v>56100</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>520625</v>
+        <v>516500</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 劉傑廷</t>
+          <t>月嫂撥款 趙強</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -800,10 +800,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="I9" t="n">
-        <v>523125</v>
+        <v>521500</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>35000</v>
+        <v>32500</v>
       </c>
       <c r="I10" t="n">
-        <v>558125</v>
+        <v>554000</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -893,11 +893,11 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>526250</v>
+        <v>522125</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 趙美</t>
+          <t>月嫂撥款 趙建美</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -935,10 +935,10 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="I12" t="n">
-        <v>528450</v>
+        <v>524125</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>63800</v>
+        <v>48000</v>
       </c>
       <c r="I13" t="n">
-        <v>592250</v>
+        <v>572125</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>56100</v>
+        <v>42500</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>536150</v>
+        <v>529625</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 郭宏</t>
+          <t>月嫂撥款 劉欣</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>2000</v>
       </c>
       <c r="I15" t="n">
-        <v>538150</v>
+        <v>531625</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>38000</v>
+        <v>28000</v>
       </c>
       <c r="I16" t="n">
-        <v>576150</v>
+        <v>559625</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>34000</v>
+        <v>25500</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>542150</v>
+        <v>534125</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 楊萱君</t>
+          <t>月嫂撥款 林芳</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>5000</v>
       </c>
       <c r="I18" t="n">
-        <v>547150</v>
+        <v>539125</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>32500</v>
       </c>
       <c r="I19" t="n">
-        <v>579650</v>
+        <v>571625</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>2200</v>
       </c>
       <c r="I20" t="n">
-        <v>581850</v>
+        <v>573825</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>52800</v>
       </c>
       <c r="I21" t="n">
-        <v>634650</v>
+        <v>626625</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>2000</v>
+        <v>4400</v>
       </c>
       <c r="I22" t="n">
-        <v>636650</v>
+        <v>631025</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>4400</v>
+        <v>2200</v>
       </c>
       <c r="I23" t="n">
-        <v>641050</v>
+        <v>633225</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="I24" t="n">
-        <v>643550</v>
+        <v>637225</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>2500</v>
       </c>
       <c r="I25" t="n">
-        <v>646050</v>
+        <v>639725</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>15000</v>
       </c>
       <c r="I26" t="n">
-        <v>661050</v>
+        <v>654725</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>3000</v>
       </c>
       <c r="I27" t="n">
-        <v>664050</v>
+        <v>657725</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>趙偉洋</t>
+          <t>李傑俊</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1682,14 +1682,14 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>75000</v>
+        <v>44000</v>
       </c>
       <c r="J1" t="n">
-        <v>63750</v>
+        <v>37400</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>趙偉洋</t>
+          <t>李傑俊</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>劉傑廷</t>
+          <t>趙強</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1732,14 +1732,14 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>62500</v>
+        <v>66000</v>
       </c>
       <c r="J2" t="n">
-        <v>53125</v>
+        <v>56100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>劉傑廷</t>
+          <t>趙強</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>趙美</t>
+          <t>趙建美</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>趙美</t>
+          <t>趙建美</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>郭宏</t>
+          <t>劉欣</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1832,14 +1832,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>66000</v>
+        <v>50000</v>
       </c>
       <c r="J4" t="n">
-        <v>56100</v>
+        <v>42500</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>郭宏</t>
+          <t>劉欣</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>楊萱君</t>
+          <t>林芳</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="J5" t="n">
-        <v>34000</v>
+        <v>25500</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>楊萱君</t>
+          <t>林芳</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>楊婷強</t>
+          <t>劉偉豪</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>楊婷強</t>
+          <t>劉偉豪</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>林嘉</t>
+          <t>蔡冠</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>林嘉</t>
+          <t>蔡冠</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>張芳</t>
+          <t>劉翔</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="J8" t="n">
-        <v>42500</v>
+        <v>46750</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>張芳</t>
+          <t>劉翔</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>楊俊</t>
+          <t>周偉</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2082,14 +2082,14 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="J9" t="n">
-        <v>28050</v>
+        <v>46750</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>楊俊</t>
+          <t>周偉</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>吳雅明</t>
+          <t>周涵</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2132,14 +2132,14 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>62500</v>
+        <v>50000</v>
       </c>
       <c r="J10" t="n">
-        <v>53125</v>
+        <v>42500</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>吳雅明</t>
+          <t>周涵</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -530,10 +530,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="I3" t="n">
-        <v>504000</v>
+        <v>502500</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>36000</v>
+        <v>35000</v>
       </c>
       <c r="I4" t="n">
-        <v>540000</v>
+        <v>537500</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>34000</v>
+        <v>31875</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>506000</v>
+        <v>505625</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 吳晴宇</t>
+          <t>月嫂撥款 蔡嘉</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -668,7 +668,7 @@
         <v>2500</v>
       </c>
       <c r="I6" t="n">
-        <v>508500</v>
+        <v>508125</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>35000</v>
+        <v>72500</v>
       </c>
       <c r="I7" t="n">
-        <v>543500</v>
+        <v>580625</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -754,15 +754,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>31875</v>
+        <v>63750</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>511625</v>
+        <v>516875</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 劉芳偉</t>
+          <t>月嫂撥款 徐華</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -800,10 +800,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="I9" t="n">
-        <v>515625</v>
+        <v>519375</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>56000</v>
+        <v>47500</v>
       </c>
       <c r="I10" t="n">
-        <v>571625</v>
+        <v>566875</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>51000</v>
+        <v>42500</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>520625</v>
+        <v>524375</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 林欣</t>
+          <t>月嫂撥款 張洋</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -935,10 +935,10 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I12" t="n">
-        <v>522625</v>
+        <v>526875</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>58000</v>
+        <v>72500</v>
       </c>
       <c r="I13" t="n">
-        <v>580625</v>
+        <v>599375</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>51000</v>
+        <v>63750</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>529625</v>
+        <v>535625</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 賴華萱</t>
+          <t>月嫂撥款 陳宥</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="I15" t="n">
-        <v>534025</v>
+        <v>538125</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>39600</v>
+        <v>35000</v>
       </c>
       <c r="I16" t="n">
-        <v>573625</v>
+        <v>573125</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>37400</v>
+        <v>31875</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>536225</v>
+        <v>541250</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 林俊美</t>
+          <t>月嫂撥款 趙冠安</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="I18" t="n">
-        <v>538425</v>
+        <v>543750</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>52800</v>
+        <v>47500</v>
       </c>
       <c r="I19" t="n">
-        <v>591225</v>
+        <v>591250</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>4400</v>
       </c>
       <c r="I20" t="n">
-        <v>595625</v>
+        <v>595650</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>61600</v>
+        <v>39600</v>
       </c>
       <c r="I21" t="n">
-        <v>657225</v>
+        <v>635250</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I22" t="n">
-        <v>661225</v>
+        <v>640250</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="I23" t="n">
-        <v>663725</v>
+        <v>642450</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>4400</v>
+        <v>4000</v>
       </c>
       <c r="I24" t="n">
-        <v>668125</v>
+        <v>646450</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>2500</v>
       </c>
       <c r="I25" t="n">
-        <v>670625</v>
+        <v>648950</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>15000</v>
       </c>
       <c r="I26" t="n">
-        <v>685625</v>
+        <v>663950</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>3000</v>
       </c>
       <c r="I27" t="n">
-        <v>688625</v>
+        <v>666950</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>吳晴宇</t>
+          <t>蔡嘉</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1682,14 +1682,14 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>40000</v>
+        <v>37500</v>
       </c>
       <c r="J1" t="n">
-        <v>34000</v>
+        <v>31875</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>吳晴宇</t>
+          <t>蔡嘉</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>劉芳偉</t>
+          <t>徐華</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1732,14 +1732,14 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>37500</v>
+        <v>75000</v>
       </c>
       <c r="J2" t="n">
-        <v>31875</v>
+        <v>63750</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>劉芳偉</t>
+          <t>徐華</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>林欣</t>
+          <t>張洋</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1782,14 +1782,14 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="J3" t="n">
-        <v>51000</v>
+        <v>42500</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>林欣</t>
+          <t>張洋</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>賴華萱</t>
+          <t>陳宥</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1832,14 +1832,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>60000</v>
+        <v>75000</v>
       </c>
       <c r="J4" t="n">
-        <v>51000</v>
+        <v>63750</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>賴華萱</t>
+          <t>陳宥</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>林俊美</t>
+          <t>趙冠安</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>44000</v>
+        <v>37500</v>
       </c>
       <c r="J5" t="n">
-        <v>37400</v>
+        <v>31875</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>林俊美</t>
+          <t>趙冠安</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>林強</t>
+          <t>張雅宏</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>55000</v>
+        <v>50000</v>
       </c>
       <c r="J6" t="n">
-        <v>46750</v>
+        <v>42500</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>林強</t>
+          <t>張雅宏</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>蔡雅</t>
+          <t>賴嘉</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1982,14 +1982,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>66000</v>
+        <v>44000</v>
       </c>
       <c r="J7" t="n">
-        <v>56100</v>
+        <v>37400</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>蔡雅</t>
+          <t>賴嘉</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>賴晴</t>
+          <t>劉豪涵</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="J8" t="n">
-        <v>34000</v>
+        <v>42500</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>賴晴</t>
+          <t>劉豪涵</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>吳明強</t>
+          <t>楊茹強</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2082,14 +2082,14 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>75000</v>
+        <v>44000</v>
       </c>
       <c r="J9" t="n">
-        <v>63750</v>
+        <v>37400</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>吳明強</t>
+          <t>楊茹強</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>李安俊</t>
+          <t>李嘉</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2132,14 +2132,14 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>44000</v>
+        <v>60000</v>
       </c>
       <c r="J10" t="n">
-        <v>37400</v>
+        <v>51000</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>李安俊</t>
+          <t>李嘉</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -530,10 +530,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="I3" t="n">
-        <v>502500</v>
+        <v>504000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="I4" t="n">
-        <v>537500</v>
+        <v>540000</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>31875</v>
+        <v>34000</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>505625</v>
+        <v>506000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 蔡嘉</t>
+          <t>月嫂撥款 劉嘉</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -668,7 +668,7 @@
         <v>2500</v>
       </c>
       <c r="I6" t="n">
-        <v>508125</v>
+        <v>508500</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>72500</v>
+        <v>47500</v>
       </c>
       <c r="I7" t="n">
-        <v>580625</v>
+        <v>556000</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -754,15 +754,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>63750</v>
+        <v>42500</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>516875</v>
+        <v>513500</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 徐華</t>
+          <t>月嫂撥款 吳威婷</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -800,10 +800,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="I9" t="n">
-        <v>519375</v>
+        <v>517500</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>47500</v>
+        <v>36000</v>
       </c>
       <c r="I10" t="n">
-        <v>566875</v>
+        <v>553500</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>524375</v>
+        <v>519500</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 張洋</t>
+          <t>月嫂撥款 胡奕</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -935,10 +935,10 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="I12" t="n">
-        <v>526875</v>
+        <v>521700</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>72500</v>
+        <v>52800</v>
       </c>
       <c r="I13" t="n">
-        <v>599375</v>
+        <v>574500</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>63750</v>
+        <v>46750</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>535625</v>
+        <v>527750</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 陳宥</t>
+          <t>月嫂撥款 林翔美</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="n">
-        <v>538125</v>
+        <v>530250</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>35000</v>
+        <v>72500</v>
       </c>
       <c r="I16" t="n">
-        <v>573125</v>
+        <v>602750</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>31875</v>
+        <v>63750</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>541250</v>
+        <v>539000</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 趙冠安</t>
+          <t>月嫂撥款 許萱</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="I18" t="n">
-        <v>543750</v>
+        <v>544000</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>47500</v>
+        <v>32500</v>
       </c>
       <c r="I19" t="n">
-        <v>591250</v>
+        <v>576500</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>4400</v>
+        <v>2000</v>
       </c>
       <c r="I20" t="n">
-        <v>595650</v>
+        <v>578500</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>39600</v>
+        <v>48000</v>
       </c>
       <c r="I21" t="n">
-        <v>635250</v>
+        <v>626500</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I22" t="n">
-        <v>640250</v>
+        <v>630500</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="I23" t="n">
-        <v>642450</v>
+        <v>632500</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>4000</v>
       </c>
       <c r="I24" t="n">
-        <v>646450</v>
+        <v>636500</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>2500</v>
       </c>
       <c r="I25" t="n">
-        <v>648950</v>
+        <v>639000</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>15000</v>
       </c>
       <c r="I26" t="n">
-        <v>663950</v>
+        <v>654000</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>3000</v>
       </c>
       <c r="I27" t="n">
-        <v>666950</v>
+        <v>657000</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>蔡嘉</t>
+          <t>劉嘉</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1682,14 +1682,14 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>37500</v>
+        <v>40000</v>
       </c>
       <c r="J1" t="n">
-        <v>31875</v>
+        <v>34000</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>蔡嘉</t>
+          <t>劉嘉</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>徐華</t>
+          <t>吳威婷</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1732,14 +1732,14 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="J2" t="n">
-        <v>63750</v>
+        <v>42500</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>徐華</t>
+          <t>吳威婷</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>張洋</t>
+          <t>胡奕</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1782,14 +1782,14 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="J3" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>張洋</t>
+          <t>胡奕</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>陳宥</t>
+          <t>林翔美</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1832,14 +1832,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>75000</v>
+        <v>55000</v>
       </c>
       <c r="J4" t="n">
-        <v>63750</v>
+        <v>46750</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>陳宥</t>
+          <t>林翔美</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>趙冠安</t>
+          <t>許萱</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>37500</v>
+        <v>75000</v>
       </c>
       <c r="J5" t="n">
-        <v>31875</v>
+        <v>63750</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>趙冠安</t>
+          <t>許萱</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>張雅宏</t>
+          <t>王晴</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>50000</v>
+        <v>37500</v>
       </c>
       <c r="J6" t="n">
-        <v>42500</v>
+        <v>31875</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>張雅宏</t>
+          <t>王晴</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>賴嘉</t>
+          <t>張廷</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1982,14 +1982,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>44000</v>
+        <v>50000</v>
       </c>
       <c r="J7" t="n">
-        <v>37400</v>
+        <v>42500</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>賴嘉</t>
+          <t>張廷</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>劉豪涵</t>
+          <t>吳美宇</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="J8" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>劉豪涵</t>
+          <t>吳美宇</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>楊茹強</t>
+          <t>周宥建</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2082,14 +2082,14 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>44000</v>
+        <v>60000</v>
       </c>
       <c r="J9" t="n">
-        <v>37400</v>
+        <v>51000</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>楊茹強</t>
+          <t>周宥建</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>李嘉</t>
+          <t>郭茹</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>李嘉</t>
+          <t>郭茹</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -530,10 +530,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>4000</v>
+        <v>2200</v>
       </c>
       <c r="I3" t="n">
-        <v>504000</v>
+        <v>502200</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>36000</v>
+        <v>52800</v>
       </c>
       <c r="I4" t="n">
-        <v>540000</v>
+        <v>555000</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>34000</v>
+        <v>46750</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>506000</v>
+        <v>508250</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 劉嘉</t>
+          <t>月嫂撥款 楊洋玲</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -665,10 +665,10 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="I6" t="n">
-        <v>508500</v>
+        <v>512250</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>47500</v>
+        <v>36000</v>
       </c>
       <c r="I7" t="n">
-        <v>556000</v>
+        <v>548250</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -754,15 +754,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>513500</v>
+        <v>514250</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 吳威婷</t>
+          <t>月嫂撥款 黃欣</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -800,10 +800,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I9" t="n">
-        <v>517500</v>
+        <v>519250</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>36000</v>
+        <v>57500</v>
       </c>
       <c r="I10" t="n">
-        <v>553500</v>
+        <v>576750</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>34000</v>
+        <v>53125</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>519500</v>
+        <v>523625</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 胡奕</t>
+          <t>月嫂撥款 李強</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -935,10 +935,10 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="I12" t="n">
-        <v>521700</v>
+        <v>525625</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>52800</v>
+        <v>38000</v>
       </c>
       <c r="I13" t="n">
-        <v>574500</v>
+        <v>563625</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>46750</v>
+        <v>34000</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>527750</v>
+        <v>529625</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 林翔美</t>
+          <t>月嫂撥款 陳建建</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>2500</v>
       </c>
       <c r="I15" t="n">
-        <v>530250</v>
+        <v>532125</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>72500</v>
+        <v>60000</v>
       </c>
       <c r="I16" t="n">
-        <v>602750</v>
+        <v>592125</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>63750</v>
+        <v>53125</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 許萱</t>
+          <t>月嫂撥款 張建涵</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="I18" t="n">
-        <v>544000</v>
+        <v>541500</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>32500</v>
+        <v>72500</v>
       </c>
       <c r="I19" t="n">
-        <v>576500</v>
+        <v>614000</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="I20" t="n">
-        <v>578500</v>
+        <v>616200</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>48000</v>
+        <v>52800</v>
       </c>
       <c r="I21" t="n">
-        <v>626500</v>
+        <v>669000</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I22" t="n">
-        <v>630500</v>
+        <v>674000</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="I23" t="n">
-        <v>632500</v>
+        <v>676200</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>4000</v>
       </c>
       <c r="I24" t="n">
-        <v>636500</v>
+        <v>680200</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>2500</v>
       </c>
       <c r="I25" t="n">
-        <v>639000</v>
+        <v>682700</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>15000</v>
       </c>
       <c r="I26" t="n">
-        <v>654000</v>
+        <v>697700</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>3000</v>
       </c>
       <c r="I27" t="n">
-        <v>657000</v>
+        <v>700700</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>劉嘉</t>
+          <t>楊洋玲</t>
         </is>
       </c>
       <c r="E1" t="n">
@@ -1682,14 +1682,14 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="J1" t="n">
-        <v>34000</v>
+        <v>46750</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>劉嘉</t>
+          <t>楊洋玲</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>吳威婷</t>
+          <t>黃欣</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1732,14 +1732,14 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="J2" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>吳威婷</t>
+          <t>黃欣</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>胡奕</t>
+          <t>李強</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1782,14 +1782,14 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>40000</v>
+        <v>62500</v>
       </c>
       <c r="J3" t="n">
-        <v>34000</v>
+        <v>53125</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>胡奕</t>
+          <t>李強</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>林翔美</t>
+          <t>陳建建</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1832,14 +1832,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>55000</v>
+        <v>40000</v>
       </c>
       <c r="J4" t="n">
-        <v>46750</v>
+        <v>34000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>林翔美</t>
+          <t>陳建建</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>許萱</t>
+          <t>張建涵</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>75000</v>
+        <v>62500</v>
       </c>
       <c r="J5" t="n">
-        <v>63750</v>
+        <v>53125</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>許萱</t>
+          <t>張建涵</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>王晴</t>
+          <t>林奕</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>37500</v>
+        <v>75000</v>
       </c>
       <c r="J6" t="n">
-        <v>31875</v>
+        <v>63750</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>王晴</t>
+          <t>林奕</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>張廷</t>
+          <t>高芳</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1982,14 +1982,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="J7" t="n">
-        <v>42500</v>
+        <v>46750</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>張廷</t>
+          <t>高芳</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>吳美宇</t>
+          <t>楊強</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="J8" t="n">
-        <v>34000</v>
+        <v>42500</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>吳美宇</t>
+          <t>楊強</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>周宥建</t>
+          <t>周茹宥</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2082,14 +2082,14 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>60000</v>
+        <v>44000</v>
       </c>
       <c r="J9" t="n">
-        <v>51000</v>
+        <v>37400</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>周宥建</t>
+          <t>周茹宥</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>郭茹</t>
+          <t>王廷</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>郭茹</t>
+          <t>王廷</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/document/資料庫、資料處理/帳務.xlsx
+++ b/document/資料庫、資料處理/帳務.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,10 +575,10 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>52800</v>
+        <v>26400</v>
       </c>
       <c r="I4" t="n">
-        <v>555000</v>
+        <v>528600</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -595,22 +595,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/07/16 16:00:00</t>
+          <t>2026/07/19 11:00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>一般轉出</t>
+          <t>虛擬帳入</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,16 +618,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>46750</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>26400</v>
+      </c>
       <c r="I5" t="n">
-        <v>508250</v>
+        <v>555000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>月嫂撥款 楊洋玲</t>
+          <t>99781699115001</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -640,22 +640,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/07/02 10:00:00</t>
+          <t>2026/07/16 16:00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>虛擬帳入</t>
+          <t>一般轉出</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -663,16 +663,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>4000</v>
-      </c>
+      <c r="G6" t="n">
+        <v>46750</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>512250</v>
+        <v>508250</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>99781699115002</t>
+          <t>月嫂撥款 楊洋玲</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -685,17 +685,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/07/12 14:00:00</t>
+          <t>2026/07/02 10:00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -710,10 +710,10 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>36000</v>
+        <v>4000</v>
       </c>
       <c r="I7" t="n">
-        <v>548250</v>
+        <v>512250</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -730,22 +730,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/07/17 16:00:00</t>
+          <t>2026/07/12 14:00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>一般轉出</t>
+          <t>虛擬帳入</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -753,16 +753,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>34000</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>18000</v>
+      </c>
       <c r="I8" t="n">
-        <v>514250</v>
+        <v>530250</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>月嫂撥款 黃欣</t>
+          <t>99781699115002</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -775,17 +775,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/07/03 10:00:00</t>
+          <t>2026/07/20 11:00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -800,14 +800,14 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="I9" t="n">
-        <v>519250</v>
+        <v>548250</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>99781699115003</t>
+          <t>99781699115002</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -820,22 +820,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/07/13 14:00:00</t>
+          <t>2026/07/17 16:00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>虛擬帳入</t>
+          <t>一般轉出</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -843,16 +843,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>57500</v>
-      </c>
+      <c r="G10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>576750</v>
+        <v>514250</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>99781699115003</t>
+          <t>月嫂撥款 黃欣</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -865,22 +865,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/07/18 16:00:00</t>
+          <t>2026/07/03 10:00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>一般轉出</t>
+          <t>虛擬帳入</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -888,16 +888,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>53125</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>5000</v>
+      </c>
       <c r="I11" t="n">
-        <v>523625</v>
+        <v>519250</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>月嫂撥款 李強</t>
+          <t>99781699115003</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -910,17 +910,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/07/04 10:00:00</t>
+          <t>2026/07/13 14:00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026/07/04</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/07/04</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -935,14 +935,14 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>2000</v>
+        <v>28750</v>
       </c>
       <c r="I12" t="n">
-        <v>525625</v>
+        <v>548000</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>99781699115004</t>
+          <t>99781699115003</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -955,17 +955,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/07/14 14:00:00</t>
+          <t>2026/07/21 11:00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>38000</v>
+        <v>28750</v>
       </c>
       <c r="I13" t="n">
-        <v>563625</v>
+        <v>576750</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>99781699115004</t>
+          <t>99781699115003</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1000,17 +1000,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/07/19 16:00:00</t>
+          <t>2026/07/18 16:00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026/07/19</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/07/19</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>34000</v>
+        <v>53125</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>529625</v>
+        <v>523625</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>月嫂撥款 陳建建</t>
+          <t>月嫂撥款 李強</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1045,17 +1045,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/07/05 10:00:00</t>
+          <t>2026/07/04 10:00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026/07/05</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/07/05</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1070,14 +1070,14 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I15" t="n">
-        <v>532125</v>
+        <v>525625</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>99781699115005</t>
+          <t>99781699115004</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1090,17 +1090,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/07/15 14:00:00</t>
+          <t>2026/07/14 14:00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1115,14 +1115,14 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>60000</v>
+        <v>19000</v>
       </c>
       <c r="I16" t="n">
-        <v>592125</v>
+        <v>544625</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>99781699115005</t>
+          <t>99781699115004</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1135,22 +1135,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/07/20 16:00:00</t>
+          <t>2026/07/22 11:00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>一般轉出</t>
+          <t>虛擬帳入</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1158,16 +1158,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>53125</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>19000</v>
+      </c>
       <c r="I17" t="n">
-        <v>539000</v>
+        <v>563625</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>月嫂撥款 張建涵</t>
+          <t>99781699115004</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/07/06 10:00:00</t>
+          <t>2026/07/19 16:00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>虛擬帳入</t>
+          <t>一般轉出</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1203,16 +1203,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>2500</v>
-      </c>
+      <c r="G18" t="n">
+        <v>34000</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>541500</v>
+        <v>529625</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>99781699115006</t>
+          <t>月嫂撥款 陳建建</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1225,17 +1225,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026/07/16 14:00:00</t>
+          <t>2026/07/05 10:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>72500</v>
+        <v>2500</v>
       </c>
       <c r="I19" t="n">
-        <v>614000</v>
+        <v>532125</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>99781699115006</t>
+          <t>99781699115005</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026/07/07 10:00:00</t>
+          <t>2026/07/15 14:00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2200</v>
+        <v>30000</v>
       </c>
       <c r="I20" t="n">
-        <v>616200</v>
+        <v>562125</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>99781699115007</t>
+          <t>99781699115005</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1315,17 +1315,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026/07/17 14:00:00</t>
+          <t>2026/07/23 11:00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1340,14 +1340,14 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>52800</v>
+        <v>30000</v>
       </c>
       <c r="I21" t="n">
-        <v>669000</v>
+        <v>592125</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>99781699115007</t>
+          <t>99781699115005</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026/07/08 10:00:00</t>
+          <t>2026/07/20 16:00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>虛擬帳入</t>
+          <t>一般轉出</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1383,16 +1383,16 @@
           <t>TWD</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>5000</v>
-      </c>
+      <c r="G22" t="n">
+        <v>53125</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>674000</v>
+        <v>539000</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>99781699115008</t>
+          <t>月嫂撥款 張建涵</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1405,17 +1405,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026/07/09 10:00:00</t>
+          <t>2026/07/06 10:00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026/07/09</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/07/09</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1430,14 +1430,14 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="I23" t="n">
-        <v>676200</v>
+        <v>541500</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>99781699115009</t>
+          <t>99781699115006</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026/07/10 10:00:00</t>
+          <t>2026/07/16 14:00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1475,14 +1475,14 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>4000</v>
+        <v>36250</v>
       </c>
       <c r="I24" t="n">
-        <v>680200</v>
+        <v>577750</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>99781699115010</t>
+          <t>99781699115006</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1495,22 +1495,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026/07/05 09:30:00</t>
+          <t>2026/07/07 10:00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026/07/05</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/07/05</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>網銀轉入</t>
+          <t>虛擬帳入</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1520,21 +1520,17 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="I25" t="n">
-        <v>682700</v>
+        <v>579950</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>99781601001001</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>托育課程費</t>
-        </is>
-      </c>
+          <t>99781699115007</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1544,22 +1540,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026/07/12 11:20:00</t>
+          <t>2026/07/17 14:00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>臨櫃存入</t>
+          <t>虛擬帳入</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1569,21 +1565,17 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>15000</v>
+        <v>26400</v>
       </c>
       <c r="I26" t="n">
-        <v>697700</v>
+        <v>606350</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12345678901234</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>常規捐款</t>
-        </is>
-      </c>
+          <t>99781699115007</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1593,17 +1585,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026/07/20 15:45:00</t>
+          <t>2026/07/08 10:00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1618,17 +1610,250 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>611350</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>99781699115008</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>03201800231313</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026/07/09 10:00:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>虛擬帳入</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I28" t="n">
+        <v>613550</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>99781699115009</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>03201800231313</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026/07/10 10:00:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>虛擬帳入</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>617550</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>99781699115010</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>03201800231313</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026/07/05 09:30:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026/07/05</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/07/05</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>網銀轉入</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I30" t="n">
+        <v>620050</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>99781601001001</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>托育課程費</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>03201800231313</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026/07/12 11:20:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026/07/12</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/07/12</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>臨櫃存入</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I31" t="n">
+        <v>635050</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>12345678901234</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>常規捐款</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>03201800231313</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026/07/20 15:45:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>虛擬帳入</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
         <v>3000</v>
       </c>
-      <c r="I27" t="n">
-        <v>700700</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="I32" t="n">
+        <v>638050</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>99781602002002</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>保母課程費</t>
         </is>
